--- a/q1.xlsx
+++ b/q1.xlsx
@@ -8,8 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Header_Guide" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$H$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Header_Guide'!$A$1:$D$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -425,16 +429,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="76" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -898,17 +902,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9 × 9 = ?</t>
+          <t>14 × 6 = ?</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9 × 9 = 81.</t>
+          <t>14 × 6 = 84.</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -916,11 +920,3871 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Q012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>17 × 5 = ?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>17 × 5 = 85.</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Q013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>18 × 7 = ?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>18 × 7 = 126.</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Q014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>26 × 3 = ?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>26 × 3 = 78.</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Q015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>31 × 4 = ?</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>31 × 4 = 124.</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Q016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>42 × 5 = ?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>42 × 5 = 210.</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>56 × 6 = ?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>56 × 6 = 336.</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Q018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>64 × 7 = ?</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>64 × 7 = 448.</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Q019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>75 × 8 = ?</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>75 × 8 = 600.</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Q020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>86 × 9 = ?</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>86 × 9 = 774.</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Q021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>12 × 12 = ?</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>12 × 12 = 144.</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>15 × 11 = ?</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>15 × 11 = 165.</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>21 × 13 = ?</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>21 × 13 = 273.</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Q024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>24 × 12 = ?</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>24 × 12 = 288.</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Q025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>32 × 11 = ?</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>32 × 11 = 352.</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>45 × 12 = ?</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>45 × 12 = 540.</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>52 × 13 = ?</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>52 × 13 = 676.</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>63 × 11 = ?</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>63 × 11 = 693.</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Q029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>72 × 12 = ?</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>72 × 12 = 864.</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>12</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>84 × 11 = ?</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>84 × 11 = 924.</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>12</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>78 ÷ 6 = ?</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Because 6 × 13 = 78.</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>98 ÷ 7 = ?</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Because 7 × 14 = 98.</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>128 ÷ 8 = ?</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Because 8 × 16 = 128.</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>12</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>162 ÷ 9 = ?</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Because 9 × 18 = 162.</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>12</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>132 ÷ 12 = ?</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Because 12 × 11 = 132.</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>12</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>180 ÷ 12 = ?</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Because 12 × 15 = 180.</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>12</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>168 ÷ 14 = ?</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Because 14 × 12 = 168.</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>12</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>195 ÷ 15 = ?</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Because 15 × 13 = 195.</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>12</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>224 ÷ 16 = ?</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Because 16 × 14 = 224.</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>12</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>216 ÷ 18 = ?</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Because 18 × 12 = 216.</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>12</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>231 ÷ 21 = ?</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Because 21 × 11 = 231.</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>12</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>288 ÷ 24 = ?</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Because 24 × 12 = 288.</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>12</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>What is the 8th multiple of 6?</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6 × 8 = 48.</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>10</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Q044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>What is the 7th multiple of 8?</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8 × 7 = 56.</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>10</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Q045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>What is the 9th multiple of 9?</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>9 × 9 = 81.</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>10</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Q046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>What is the 6th multiple of 11?</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>11 × 6 = 66.</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>10</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Q047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>What is the 8th multiple of 12?</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>12 × 8 = 96.</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>10</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Q048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>What is the 7th multiple of 13?</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>13 × 7 = 91.</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>10</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Q049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>What is the 6th multiple of 15?</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>15 × 6 = 90.</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>10</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Q050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>What is the 5th multiple of 16?</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>16 × 5 = 80.</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>10</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Q051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>What is the 4th multiple of 18?</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>18 × 4 = 72.</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>10</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Q052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>What is the 4th multiple of 25?</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>25 × 4 = 100.</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>10</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Q053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>How many factors does 18 have?</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>The factors are 1, 2, 3, 6, 9, 18, so there are 6 factors.</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>15</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Q054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>How many factors does 20 have?</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>The factors are 1, 2, 4, 5, 10, 20, so there are 6 factors.</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>15</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Q055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>How many factors does 28 have?</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>The factors are 1, 2, 4, 7, 14, 28, so there are 6 factors.</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>15</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Q056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>How many factors does 30 have?</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>The factors are 1, 2, 3, 5, 6, 10, 15, 30, so there are 8 factors.</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>15</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Q057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>How many factors does 36 have?</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>The factors are 1, 2, 3, 4, 6, 9, 12, 18, 36, so there are 9 factors.</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>15</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Q058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>How many factors does 40 have?</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>The factors are 1, 2, 4, 5, 8, 10, 20, 40, so there are 8 factors.</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>15</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Q059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>How many factors does 42 have?</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>The factors are 1, 2, 3, 6, 7, 14, 21, 42, so there are 8 factors.</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>15</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Q060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>How many factors does 48 have?</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>The factors are 1, 2, 3, 4, 6, 8, 12, 16, 24, 48, so there are 10 factors.</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>15</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Q061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>How many factors does 56 have?</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>The factors are 1, 2, 4, 7, 8, 14, 28, 56, so there are 8 factors.</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>15</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Q062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>How many factors does 60 have?</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>The factors are 1, 2, 3, 4, 5, 6, 10, 12, 15, 20, 30, 60, so there are 12 factors.</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>15</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Q063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>How many factors does 72 have?</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>The factors are 1, 2, 3, 4, 6, 8, 9, 12, 18, 24, 36, 72, so there are 12 factors.</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>15</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Q064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Multiples and Factors</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>How many factors does 84 have?</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>The factors are 1, 2, 3, 4, 6, 7, 12, 14, 21, 28, 42, 84, so there are 12 factors.</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>15</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Q065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1/8 + 3/8 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1/8 + 3/8 = 4/8, which simplifies to 1/2.</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>15</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Q066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2/9 + 4/9 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2/9 + 4/9 = 6/9, which simplifies to 2/3.</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>15</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Q067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3/10 + 5/10 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3/10 + 5/10 = 8/10, which simplifies to 4/5.</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>15</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Q068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>4/12 + 2/12 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>4/12 + 2/12 = 6/12, which simplifies to 1/2.</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>15</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Q069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>5/14 + 3/14 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>5/14 + 3/14 = 8/14, which simplifies to 4/7.</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>15</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Q070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>7/8 - 3/8 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>7/8 - 3/8 = 4/8, which simplifies to 1/2.</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>15</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Q071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>9/10 - 4/10 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>9/10 - 4/10 = 5/10, which simplifies to 1/2.</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>15</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Q072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>11/12 - 5/12 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>11/12 - 5/12 = 6/12, which simplifies to 1/2.</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>15</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Q073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>13/15 - 4/15 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>13/15 - 4/15 = 9/15, which simplifies to 3/5.</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>15</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Q074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>17/20 - 7/20 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>17/20 - 7/20 = 10/20, which simplifies to 1/2.</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Q075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3/6 + 2/6 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>3/6 + 2/6 = 5/6.</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>15</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Q076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4/8 + 2/8 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>4/8 + 2/8 = 6/8, which simplifies to 3/4.</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>15</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Q077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>6/9 + 1/9 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>7/9</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>6/9 + 1/9 = 7/9.</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>15</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Q078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>5/12 + 3/12 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>5/12 + 3/12 = 8/12, which simplifies to 2/3.</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>15</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Q079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>7/16 + 5/16 = ? Simplify if needed.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>7/16 + 5/16 = 12/16, which simplifies to 3/4.</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>15</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Q080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3.4 + 2.5 = ?</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 3.4 + 2.5 = 5.9.</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>10</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Q081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>5.7 + 1.8 = ?</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 5.7 + 1.8 = 7.5.</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>10</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Q082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>6.6 + 3.9 = ?</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 6.6 + 3.9 = 10.5.</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>10</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Q083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>8.4 + 4.7 = ?</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 8.4 + 4.7 = 13.1.</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>10</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Q084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>12.5 + 6.8 = ?</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 12.5 + 6.8 = 19.3.</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>12</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Q085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>9.6 - 2.4 = ?</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 9.6 - 2.4 = 7.2.</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>10</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Q086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>10.5 - 3.8 = ?</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 10.5 - 3.8 = 6.7.</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>12</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Q087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>14.2 - 5.7 = ?</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 14.2 - 5.7 = 8.5.</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>12</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Q088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>18.6 - 9.9 = ?</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 18.6 - 9.9 = 8.7.</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>12</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Q089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>20 - 7.5 = ?</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 20 - 7.5 = 12.5.</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>12</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Q090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2.35 + 1.4 = ?</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 2.35 + 1.4 = 3.75.</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>10</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Q091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>4.75 + 2.25 = ?</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 4.75 + 2.25 = 7.</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>10</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Q092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>8.6 - 3.45 = ?</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 8.6 - 3.45 = 5.15.</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>10</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Q093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>12.3 - 4.85 = ?</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>7.45</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 12.3 - 4.85 = 7.45.</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>12</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Q094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>15.75 - 6.6 = ?</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>9.15</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Line up the decimal places: 15.75 - 6.6 = 9.15.</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>12</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Q095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Word Problems</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>A student buys 4 exercise books at HK$12 each. How much does the student pay in total?</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>4 × 12 = 48, so the total is HK$48.</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>15</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Q096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Word Problems</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>There are 6 rows of chairs in a classroom. Each row has 8 chairs. How many chairs are there altogether?</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>6 × 8 = 48.</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>15</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Q097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Word Problems</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>A minibus has 16 seats. How many seats are there in 7 minibuses?</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>16 × 7 = 112.</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>15</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Q098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Word Problems</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>A shop packs 96 pencils equally into 8 boxes. How many pencils are in each box?</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>96 ÷ 8 = 12.</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>15</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Q099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Word Problems</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>A class collects 168 stickers and shares them equally among 12 groups. How many stickers does each group get?</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>168 ÷ 12 = 14.</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>18</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Q100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Word Problems</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>A student spends HK$15.50 on a drink and HK$8.20 on a snack. How much is spent altogether?</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>15.50 + 8.20 = 23.70, so the answer is 23.7.</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>18</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Q101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Word Problems</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>A book costs HK$58. A student pays with HK$100. How much change should the student get?</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>100 - 58 = 42.</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>15</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Q102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Word Problems</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>A bus ride is 12.5 km and an MTR ride is 8.7 km. How much longer is the bus ride?</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>12.5 - 8.7 = 3.8 km.</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>18</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H103"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QuestionID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unique question code</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Q001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Difficulty level</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Easy / Medium / Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Topic filter shown in game</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Multiplication</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QuestionText</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Question displayed to students</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12 × 8 = ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Exact answer used for checking</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Explanation</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Feedback shown after wrong answer or timeout</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>12 × 8 = 96</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TimeLimitSeconds</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Question-level timer override</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Y = use question, N = hide question</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>